--- a/appOrcam/static/arquivos/Preco_m2 esfiha e kibe Onda E (version 1).xlsx
+++ b/appOrcam/static/arquivos/Preco_m2 esfiha e kibe Onda E (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\Documents\GitHub\Dj_srcx_Orcamento\appOrcam\static\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{67104773-8CEF-4B4D-AC58-7EBB2617B750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{AF721066-096F-430E-84A5-B00074874F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{67754E85-EF51-4CB9-B61E-3CED47B47D87}"/>
   </bookViews>
@@ -222,7 +222,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="23">
+  <numFmts count="24">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0\ &quot;     unid/chapa&quot;\ "/>
@@ -244,10 +244,11 @@
     <numFmt numFmtId="181" formatCode="&quot;R$&quot;\ #,##0.00\ &quot;preço final com margem por unidade&quot;"/>
     <numFmt numFmtId="182" formatCode="&quot;R$&quot;\ #,##0.000\ &quot;por chapa&quot;"/>
     <numFmt numFmtId="184" formatCode="&quot;R$&quot;\ #,##0.000\ &quot;seladora&quot;"/>
+    <numFmt numFmtId="185" formatCode="&quot;R$&quot;\ #,##0.000"/>
     <numFmt numFmtId="186" formatCode="#,##0\ &quot;unidades&quot;"/>
     <numFmt numFmtId="187" formatCode="&quot;Csuto de fabricação: &quot;\ &quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,13 +400,6 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1108,7 +1102,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1339,21 +1333,17 @@
     <xf numFmtId="0" fontId="20" fillId="36" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="43" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="20" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1373,9 +1363,19 @@
     <xf numFmtId="187" fontId="16" fillId="38" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="38" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="16" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="187" fontId="16" fillId="38" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="185" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1440,23 +1440,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>685801</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1381126</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="Retângulo 10">
+        <xdr:cNvPr id="18" name="Retângulo 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09B8F22E-9698-8D1D-44CD-633EE2908B2D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFD3FD65-4AEC-143E-759D-94C734B1F6A6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1464,7 +1464,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1295401" y="2562225"/>
+          <a:off x="3228976" y="2609850"/>
           <a:ext cx="1409700" cy="342900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1492,6 +1492,69 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>24654</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>139513</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1437155</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>25213</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Retângulo 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09B8F22E-9698-8D1D-44CD-633EE2908B2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1346948" y="2627219"/>
+          <a:ext cx="1412501" cy="345141"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1559,15 +1622,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
+      <xdr:colOff>657226</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>121583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>685801</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>24655</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>100013</xdr:rowOff>
+      <xdr:rowOff>100012</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1585,12 +1648,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000" flipV="1">
-          <a:off x="1266825" y="2733675"/>
-          <a:ext cx="28576" cy="3348038"/>
+          <a:off x="1262344" y="2799789"/>
+          <a:ext cx="84605" cy="3373811"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 899972"/>
+            <a:gd name="adj1" fmla="val 370197"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -1616,75 +1679,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="Retângulo 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFD3FD65-4AEC-143E-759D-94C734B1F6A6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3248026" y="2571750"/>
-          <a:ext cx="1409700" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>670112</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>723901</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>109538</xdr:rowOff>
+      <xdr:colOff>727263</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>98333</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1695,20 +1699,17 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="18" idx="0"/>
-          <a:endCxn id="27" idx="1"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipH="1" flipV="1">
-          <a:off x="654844" y="3174206"/>
-          <a:ext cx="3900488" cy="2695576"/>
+          <a:off x="643359" y="3443428"/>
+          <a:ext cx="3943070" cy="2679327"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector4">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -5861"/>
-            <a:gd name="adj2" fmla="val 131096"/>
+            <a:gd name="adj1" fmla="val -5804"/>
+            <a:gd name="adj2" fmla="val 108541"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -3618,19 +3619,19 @@
     <col min="9" max="9" width="30.140625" customWidth="1"/>
     <col min="10" max="10" width="24.140625" customWidth="1"/>
     <col min="11" max="11" width="26.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="36.42578125" customWidth="1"/>
+    <col min="12" max="12" width="39" customWidth="1"/>
+    <col min="13" max="13" width="47.140625" customWidth="1"/>
     <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="M2" s="100"/>
-      <c r="N2" s="101" t="s">
+      <c r="M2" s="96"/>
+      <c r="N2" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="100"/>
-      <c r="P2" s="100"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -3654,16 +3655,16 @@
       <c r="J3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="101" t="s">
+      <c r="M3" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="N3" s="101" t="s">
+      <c r="N3" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="101" t="s">
+      <c r="O3" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="101" t="s">
+      <c r="P3" s="97" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3690,7 +3691,7 @@
         <f>+P4-I4/100*D4/100-I4/100*E4/100</f>
         <v>0.23449999999999999</v>
       </c>
-      <c r="K4" s="100" t="s">
+      <c r="K4" s="96" t="s">
         <v>6</v>
       </c>
       <c r="L4" t="s">
@@ -3733,7 +3734,7 @@
         <f>+P5-0.01*D5/100-0.01*E5/100</f>
         <v>0.308</v>
       </c>
-      <c r="K5" s="100" t="s">
+      <c r="K5" s="96" t="s">
         <v>8</v>
       </c>
       <c r="L5" t="s">
@@ -3776,7 +3777,7 @@
         <f>+P6-0.01*D6/100-0.01*E6/100</f>
         <v>0.39150000000000001</v>
       </c>
-      <c r="K6" s="100" t="s">
+      <c r="K6" s="96" t="s">
         <v>9</v>
       </c>
       <c r="L6" t="s">
@@ -3819,7 +3820,7 @@
         <f>+P7-0.01*D7/100-0.01*E7/100</f>
         <v>0.48499999999999999</v>
       </c>
-      <c r="K7" s="100" t="s">
+      <c r="K7" s="96" t="s">
         <v>10</v>
       </c>
       <c r="L7" t="s">
@@ -3862,7 +3863,7 @@
         <f>+P8-0.01*D8/100-0.01*E8/100</f>
         <v>0.58850000000000013</v>
       </c>
-      <c r="K8" s="100" t="s">
+      <c r="K8" s="96" t="s">
         <v>11</v>
       </c>
       <c r="L8" t="s">
@@ -3903,14 +3904,14 @@
     </row>
     <row r="11" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="88">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D12" s="23"/>
       <c r="H12" s="88">
         <f>+C11</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
@@ -3918,10 +3919,10 @@
       <c r="D13" s="23"/>
     </row>
     <row r="14" spans="2:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="C14" s="98" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="106" t="s">
+      <c r="C14" s="94" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="102" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3942,20 +3943,20 @@
     <row r="17" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C17" s="32">
         <f>+(VLOOKUP(C6,$K$4:$P$8,6,0)/$C$11)*VLOOKUP(C14,$L$4:$P$8,4,0)*IF(C11&gt;1,2,1)</f>
-        <v>0.59130000000000005</v>
+        <v>1.1826000000000001</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="20"/>
       <c r="H17" s="32">
-        <f>+(P6/$H$12)*VLOOKUP(C14,$L$4:$P$8,4,0)*IF(H12&gt;1,2,1)</f>
-        <v>0.59130000000000005</v>
+        <f>+C17</f>
+        <v>1.1826000000000001</v>
       </c>
       <c r="I17" s="33"/>
       <c r="J17" s="20"/>
-      <c r="L17" s="99">
-        <v>1000</v>
-      </c>
-      <c r="M17" s="99"/>
+      <c r="L17" s="95">
+        <v>600</v>
+      </c>
+      <c r="M17" s="95"/>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C18" s="24"/>
@@ -3984,14 +3985,18 @@
     <row r="21" spans="3:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C21" s="34">
         <f>SUM(C17:D19)</f>
-        <v>0.79130000000000011</v>
+        <v>1.3826000000000001</v>
       </c>
       <c r="D21" s="35"/>
       <c r="H21" s="34">
         <f>SUM(H17:I19)</f>
-        <v>0.79130000000000011</v>
+        <v>1.3826000000000001</v>
       </c>
       <c r="I21" s="35"/>
+      <c r="L21" s="107">
+        <f>+H21</f>
+        <v>1.3826000000000001</v>
+      </c>
     </row>
     <row r="23" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="3:13" x14ac:dyDescent="0.25">
@@ -3999,9 +4004,9 @@
         <f>CONCATENATE("Custos de impressão + Corte para ",$C$28," 
 capac_nominal: ",VLOOKUP($C$28,$L$4:$N$9,3,0)," chapa/hora
 pedido de ",VLOOKUP($C$28,$L$4:$N$9,3,0)," caixas")</f>
-        <v>Custos de impressão + Corte para Flexo 
-capac_nominal: 1000 chapa/hora
-pedido de 1000 caixas</v>
+        <v>Custos de impressão + Corte para Wonder 2 
+capac_nominal: 600 chapa/hora
+pedido de 600 caixas</v>
       </c>
       <c r="D24" s="82"/>
       <c r="E24" s="82"/>
@@ -4010,9 +4015,9 @@
         <f>CONCATENATE("Custos de impressão + Corte para ",$C$28," 
 capac_nominal: ",VLOOKUP($C$28,$L$4:$N$9,3,0)," chapa/hora
 pedido de ",L17," caixas")</f>
-        <v>Custos de impressão + Corte para Flexo 
-capac_nominal: 1000 chapa/hora
-pedido de 1000 caixas</v>
+        <v>Custos de impressão + Corte para Wonder 2 
+capac_nominal: 600 chapa/hora
+pedido de 600 caixas</v>
       </c>
       <c r="I24" s="82"/>
       <c r="J24" s="82"/>
@@ -4044,6 +4049,9 @@
       <c r="I26" s="37"/>
       <c r="J26" s="37"/>
       <c r="K26" s="38"/>
+      <c r="M26" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="27" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C27" s="39"/>
@@ -4052,45 +4060,48 @@
       <c r="H27" s="39"/>
       <c r="J27" s="40"/>
       <c r="K27" s="41"/>
-      <c r="M27" t="s">
-        <v>47</v>
+      <c r="M27" s="89">
+        <v>600</v>
       </c>
     </row>
     <row r="28" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C28" s="108" t="str">
+      <c r="C28" s="104" t="str">
         <f>+C14</f>
-        <v>Flexo</v>
+        <v>Wonder 2</v>
       </c>
       <c r="D28" s="42">
         <f>+$F$10/VLOOKUP(C28,$L$4:$N$9,3,0)</f>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="E28" s="43">
         <f>+D28*VLOOKUP(C28,$L$4:$M$9,2,0)</f>
-        <v>0.44279999999999997</v>
+        <v>1.034</v>
       </c>
       <c r="F28" s="44">
         <f>+$E$28/C11</f>
-        <v>0.11069999999999999</v>
+        <v>1.034</v>
       </c>
       <c r="H28" s="81" t="str">
         <f>+C14</f>
-        <v>Flexo</v>
+        <v>Wonder 2</v>
       </c>
       <c r="I28" s="42">
         <f>+$F$10/VLOOKUP(H28,$L$4:$N$9,3,0)</f>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="J28" s="43">
         <f>+I28*VLOOKUP(H28,$L$4:$M$9,2,0)</f>
-        <v>0.44279999999999997</v>
+        <v>1.034</v>
       </c>
       <c r="K28" s="44">
         <f>+$J$28/H12</f>
-        <v>0.11069999999999999</v>
-      </c>
-      <c r="M28" s="89">
-        <f>VLOOKUP(H28,$L$4:$N$9,3,0)</f>
+        <v>1.034</v>
+      </c>
+      <c r="L28" s="108">
+        <f>+K28*M27/M28</f>
+        <v>0.62039999999999995</v>
+      </c>
+      <c r="M28" s="18">
         <v>1000</v>
       </c>
     </row>
@@ -4103,17 +4114,12 @@
       <c r="I29" s="40"/>
       <c r="J29" s="40"/>
       <c r="K29" s="41"/>
-      <c r="L29" s="97">
-        <f>+M28*K28/M29</f>
-        <v>0.11069999999999999</v>
-      </c>
-      <c r="M29" s="18">
-        <f>+L17</f>
-        <v>1000</v>
+      <c r="M29" s="89">
+        <v>2500</v>
       </c>
     </row>
     <row r="30" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="107" t="str">
+      <c r="C30" s="103" t="str">
         <f>IF(D14&lt;&gt;"",D14,"")</f>
         <v>Century</v>
       </c>
@@ -4127,7 +4133,7 @@
       </c>
       <c r="F30" s="46">
         <f>+E30/$C$11*IF($C$11&gt;1,2,1)</f>
-        <v>3.5400000000000001E-2</v>
+        <v>7.0800000000000002E-2</v>
       </c>
       <c r="H30" s="67" t="str">
         <f>IF(D14&lt;&gt;"",D14,"")</f>
@@ -4143,32 +4149,35 @@
       </c>
       <c r="K30" s="46">
         <f>+J30/$H$12*IF($H$12&gt;1,2,1)</f>
-        <v>3.5400000000000001E-2</v>
-      </c>
-      <c r="M30" s="90"/>
+        <v>7.0800000000000002E-2</v>
+      </c>
+      <c r="L30" s="108">
+        <f>+(K30*M29/M30)</f>
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="M30" s="18">
+        <v>1000</v>
+      </c>
     </row>
     <row r="31" spans="3:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="49">
         <f>SUM(F28:F30)</f>
-        <v>0.14610000000000001</v>
+        <v>1.1048</v>
       </c>
       <c r="D31" s="50"/>
       <c r="E31" s="47"/>
       <c r="F31" s="48"/>
       <c r="H31" s="49">
         <f>SUM(K28:K30)</f>
-        <v>0.14610000000000001</v>
+        <v>1.1048</v>
       </c>
       <c r="I31" s="50"/>
       <c r="J31" s="47"/>
       <c r="K31" s="48"/>
-      <c r="M31" s="95">
-        <f>+K30+L29</f>
-        <v>0.14610000000000001</v>
-      </c>
+      <c r="L31" s="109"/>
     </row>
     <row r="32" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M32" s="94"/>
+      <c r="M32" s="92"/>
     </row>
     <row r="33" spans="3:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C33" s="36" t="s">
@@ -4193,6 +4202,9 @@
       <c r="I34" s="40"/>
       <c r="J34" s="40"/>
       <c r="K34" s="41"/>
+      <c r="M34" s="89">
+        <v>5000</v>
+      </c>
     </row>
     <row r="35" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C35" s="67" t="str">
@@ -4227,16 +4239,22 @@
         <f>+J35*VLOOKUP(H35,$L$4:$M$9,2,0)</f>
         <v>7.0799999999999995E-3</v>
       </c>
-      <c r="M35" s="91"/>
+      <c r="L35" s="108">
+        <f>+(K35*M34/M35)</f>
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="M35" s="18">
+        <v>1000</v>
+      </c>
     </row>
     <row r="36" spans="3:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="102">
+      <c r="C36" s="98">
         <f>SUM(F35)</f>
         <v>7.0799999999999995E-3</v>
       </c>
-      <c r="D36" s="103"/>
-      <c r="E36" s="103"/>
-      <c r="F36" s="104"/>
+      <c r="D36" s="99"/>
+      <c r="E36" s="99"/>
+      <c r="F36" s="100"/>
       <c r="H36" s="68">
         <f>SUM(K35)</f>
         <v>7.0799999999999995E-3</v>
@@ -4244,26 +4262,27 @@
       <c r="I36" s="69"/>
       <c r="J36" s="69"/>
       <c r="K36" s="70"/>
-      <c r="M36" s="96">
-        <f>+H36</f>
-        <v>7.0799999999999995E-3</v>
-      </c>
+      <c r="M36" s="93"/>
     </row>
     <row r="37" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C37" s="105">
+      <c r="C37" s="101">
         <f>+C36+C31</f>
-        <v>0.15318000000000001</v>
-      </c>
-      <c r="D37" s="105"/>
-      <c r="E37" s="105"/>
-      <c r="F37" s="105"/>
-      <c r="H37" s="105">
+        <v>1.11188</v>
+      </c>
+      <c r="D37" s="101"/>
+      <c r="E37" s="101"/>
+      <c r="F37" s="101"/>
+      <c r="H37" s="101">
         <f>+H36+H31</f>
-        <v>0.15318000000000001</v>
-      </c>
-      <c r="I37" s="105"/>
-      <c r="J37" s="105"/>
-      <c r="K37" s="105"/>
+        <v>1.11188</v>
+      </c>
+      <c r="I37" s="101"/>
+      <c r="J37" s="101"/>
+      <c r="K37" s="101"/>
+      <c r="L37" s="105"/>
+      <c r="M37" s="105"/>
+      <c r="N37" s="105"/>
+      <c r="O37" s="105"/>
     </row>
     <row r="38" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="3:16" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4279,6 +4298,10 @@
       <c r="I39" s="53"/>
       <c r="J39" s="53"/>
       <c r="K39" s="54"/>
+      <c r="L39" s="51">
+        <f>+H39</f>
+        <v>0.3</v>
+      </c>
       <c r="M39" s="51">
         <f>+H39</f>
         <v>0.3</v>
@@ -4288,21 +4311,25 @@
     <row r="41" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C41" s="55">
         <f>+C21+C31+C36+C39</f>
-        <v>1.24448</v>
+        <v>2.7944800000000001</v>
       </c>
       <c r="D41" s="56"/>
       <c r="E41" s="56"/>
       <c r="F41" s="57"/>
       <c r="H41" s="55">
         <f>+H21+H31+H36+H39</f>
-        <v>1.24448</v>
+        <v>2.7944800000000001</v>
       </c>
       <c r="I41" s="56"/>
       <c r="J41" s="56"/>
       <c r="K41" s="57"/>
+      <c r="L41" s="110">
+        <f>SUM(L28:L30,L35,L39+L21)</f>
+        <v>2.5154000000000001</v>
+      </c>
       <c r="M41" s="55">
-        <f>+H21+M31+M36+M39</f>
-        <v>1.24448</v>
+        <f>+H21+M30+M36+M39</f>
+        <v>1001.6826</v>
       </c>
       <c r="N41" s="56"/>
       <c r="O41" s="56"/>
@@ -4322,7 +4349,7 @@
       <c r="I43" s="59"/>
       <c r="J43" s="59"/>
       <c r="K43" s="60"/>
-      <c r="M43" s="92">
+      <c r="M43" s="90">
         <f>+H43</f>
         <v>0.1</v>
       </c>
@@ -4331,14 +4358,14 @@
     <row r="45" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C45" s="73" t="str">
         <f>CONCATENATE("Custos de impressão + Corte para ",$C$28," - capac_nominal: ",VLOOKUP($C$28,$L$4:$N$9,3,0)," chapa/hora")</f>
-        <v>Custos de impressão + Corte para Flexo - capac_nominal: 1000 chapa/hora</v>
+        <v>Custos de impressão + Corte para Wonder 2 - capac_nominal: 600 chapa/hora</v>
       </c>
       <c r="D45" s="74"/>
       <c r="E45" s="74"/>
       <c r="F45" s="75"/>
       <c r="H45" s="73" t="str">
         <f>CONCATENATE("Custos de impressão + Corte para ",H28," - capac_nominal: ",VLOOKUP(H28,$L$4:$N$9,3,0)," chapa/hora")</f>
-        <v>Custos de impressão + Corte para Flexo - capac_nominal: 1000 chapa/hora</v>
+        <v>Custos de impressão + Corte para Wonder 2 - capac_nominal: 600 chapa/hora</v>
       </c>
       <c r="I45" s="74"/>
       <c r="J45" s="74"/>
@@ -4379,31 +4406,32 @@
     <row r="48" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C48" s="61">
         <f>+C41/(1-C43)</f>
-        <v>1.3827555555555555</v>
+        <v>3.1049777777777776</v>
       </c>
       <c r="D48" s="62"/>
       <c r="E48" s="62"/>
       <c r="F48" s="63"/>
       <c r="H48" s="61">
         <f>+H41/(1-H43)</f>
-        <v>1.3827555555555555</v>
+        <v>3.1049777777777776</v>
       </c>
       <c r="I48" s="62"/>
       <c r="J48" s="62"/>
       <c r="K48" s="63"/>
+      <c r="L48" s="106">
+        <f>+L41*(1+H43)</f>
+        <v>2.7669400000000004</v>
+      </c>
       <c r="M48" s="61">
         <f>+M41/(1-M43)</f>
-        <v>1.3827555555555555</v>
+        <v>1112.9806666666666</v>
       </c>
       <c r="N48" s="62"/>
       <c r="O48" s="62"/>
       <c r="P48" s="63"/>
     </row>
     <row r="49" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L49" s="93">
-        <f>(M48-H48)/H48</f>
-        <v>0</v>
-      </c>
+      <c r="L49" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="37">

--- a/appOrcam/static/arquivos/Preco_m2 esfiha e kibe Onda E (version 1).xlsx
+++ b/appOrcam/static/arquivos/Preco_m2 esfiha e kibe Onda E (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\Documents\GitHub\Dj_srcx_Orcamento\appOrcam\static\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{AF721066-096F-430E-84A5-B00074874F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{84A79ADB-0EF6-401E-8379-A426B6C19800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{67754E85-EF51-4CB9-B61E-3CED47B47D87}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>Custos Unitários de materiais</t>
+  </si>
+  <si>
+    <t>área total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">área aparas </t>
   </si>
 </sst>
 </file>
@@ -245,10 +251,10 @@
     <numFmt numFmtId="182" formatCode="&quot;R$&quot;\ #,##0.000\ &quot;por chapa&quot;"/>
     <numFmt numFmtId="184" formatCode="&quot;R$&quot;\ #,##0.000\ &quot;seladora&quot;"/>
     <numFmt numFmtId="185" formatCode="&quot;R$&quot;\ #,##0.000"/>
-    <numFmt numFmtId="186" formatCode="#,##0\ &quot;unidades&quot;"/>
     <numFmt numFmtId="187" formatCode="&quot;Csuto de fabricação: &quot;\ &quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="188" formatCode="&quot;Capac_nominal: &quot;#,##0\ &quot;unidades&quot;"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -427,8 +433,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -644,6 +657,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="35">
     <border>
@@ -1102,7 +1127,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1336,7 +1361,6 @@
     <xf numFmtId="167" fontId="21" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="180" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="43" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1369,11 +1393,13 @@
     <xf numFmtId="187" fontId="16" fillId="38" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="185" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="24" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="20" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="185" fontId="20" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="185" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="20" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1680,15 +1706,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>670112</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>110941</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>727263</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>98333</xdr:rowOff>
+      <xdr:colOff>704851</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>87129</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1703,13 +1729,13 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipH="1" flipV="1">
-          <a:off x="643359" y="3443428"/>
+          <a:off x="620947" y="3230518"/>
           <a:ext cx="3943070" cy="2679327"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector4">
           <a:avLst>
             <a:gd name="adj1" fmla="val -5804"/>
-            <a:gd name="adj2" fmla="val 108541"/>
+            <a:gd name="adj2" fmla="val 121506"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -3619,19 +3645,22 @@
     <col min="9" max="9" width="30.140625" customWidth="1"/>
     <col min="10" max="10" width="24.140625" customWidth="1"/>
     <col min="11" max="11" width="26.42578125" customWidth="1"/>
-    <col min="12" max="12" width="39" customWidth="1"/>
+    <col min="12" max="12" width="45.85546875" customWidth="1"/>
     <col min="13" max="13" width="47.140625" customWidth="1"/>
     <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="M2" s="96"/>
-      <c r="N2" s="97" t="s">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="M2" s="95"/>
+      <c r="N2" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="96"/>
-      <c r="P2" s="96"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -3649,22 +3678,25 @@
       <c r="F3" t="s">
         <v>4</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="I3" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="97" t="s">
+        <v>54</v>
+      </c>
+      <c r="M3" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="N3" s="97" t="s">
+      <c r="N3" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="97" t="s">
+      <c r="O3" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="97" t="s">
+      <c r="P3" s="96" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3684,14 +3716,14 @@
       <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="1">
+      <c r="H4" s="1">
         <v>1</v>
       </c>
-      <c r="J4" s="1">
-        <f>+P4-I4/100*D4/100-I4/100*E4/100</f>
-        <v>0.23449999999999999</v>
-      </c>
-      <c r="K4" s="96" t="s">
+      <c r="J4" s="3">
+        <f>((D4-2*$G$2)*(E4-2*$G$2))/10000</f>
+        <v>0.22439999999999999</v>
+      </c>
+      <c r="K4" s="95" t="s">
         <v>6</v>
       </c>
       <c r="L4" t="s">
@@ -3704,7 +3736,7 @@
         <v>1000</v>
       </c>
       <c r="O4" s="1">
-        <v>2.92</v>
+        <v>1.78</v>
       </c>
       <c r="P4" s="3">
         <f>+D4/100*E4/100</f>
@@ -3727,14 +3759,14 @@
       <c r="F5" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="1">
+      <c r="H5" s="1">
         <v>1</v>
       </c>
-      <c r="J5" s="1">
-        <f>+P5-0.01*D5/100-0.01*E5/100</f>
-        <v>0.308</v>
-      </c>
-      <c r="K5" s="96" t="s">
+      <c r="J5" s="3">
+        <f t="shared" ref="J5:J8" si="0">((D5-2*$G$2)*(E5-2*$G$2))/10000</f>
+        <v>0.2964</v>
+      </c>
+      <c r="K5" s="95" t="s">
         <v>8</v>
       </c>
       <c r="L5" t="s">
@@ -3747,7 +3779,7 @@
         <v>600</v>
       </c>
       <c r="O5" s="1">
-        <v>2.92</v>
+        <v>1.78</v>
       </c>
       <c r="P5" s="3">
         <f>+D5/100*E5/100</f>
@@ -3770,14 +3802,14 @@
       <c r="F6" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="1">
+      <c r="H6" s="1">
         <v>1</v>
       </c>
-      <c r="J6" s="1">
-        <f>+P6-0.01*D6/100-0.01*E6/100</f>
-        <v>0.39150000000000001</v>
-      </c>
-      <c r="K6" s="96" t="s">
+      <c r="J6" s="3">
+        <f t="shared" si="0"/>
+        <v>0.37840000000000001</v>
+      </c>
+      <c r="K6" s="95" t="s">
         <v>9</v>
       </c>
       <c r="L6" t="s">
@@ -3790,7 +3822,7 @@
         <v>600</v>
       </c>
       <c r="O6" s="1">
-        <v>2.92</v>
+        <v>1.78</v>
       </c>
       <c r="P6" s="3">
         <f>+D6/100*E6/100</f>
@@ -3813,14 +3845,14 @@
       <c r="F7" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="1">
+      <c r="H7" s="1">
         <v>1</v>
       </c>
-      <c r="J7" s="1">
-        <f>+P7-0.01*D7/100-0.01*E7/100</f>
-        <v>0.48499999999999999</v>
-      </c>
-      <c r="K7" s="96" t="s">
+      <c r="J7" s="3">
+        <f t="shared" si="0"/>
+        <v>0.47039999999999998</v>
+      </c>
+      <c r="K7" s="95" t="s">
         <v>10</v>
       </c>
       <c r="L7" t="s">
@@ -3833,7 +3865,7 @@
         <v>2500</v>
       </c>
       <c r="O7" s="1">
-        <v>2.92</v>
+        <v>1.78</v>
       </c>
       <c r="P7" s="3">
         <f>+D7/100*E7/100</f>
@@ -3856,14 +3888,14 @@
       <c r="F8" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="1">
+      <c r="H8" s="1">
         <v>1</v>
       </c>
-      <c r="J8" s="1">
-        <f>+P8-0.01*D8/100-0.01*E8/100</f>
-        <v>0.58850000000000013</v>
-      </c>
-      <c r="K8" s="96" t="s">
+      <c r="J8" s="3">
+        <f t="shared" si="0"/>
+        <v>0.57240000000000002</v>
+      </c>
+      <c r="K8" s="95" t="s">
         <v>11</v>
       </c>
       <c r="L8" t="s">
@@ -3876,7 +3908,7 @@
         <v>5000</v>
       </c>
       <c r="O8" s="1">
-        <v>2.92</v>
+        <v>1.78</v>
       </c>
       <c r="P8" s="3">
         <f>+D8/100*E8/100</f>
@@ -3919,10 +3951,10 @@
       <c r="D13" s="23"/>
     </row>
     <row r="14" spans="2:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="C14" s="94" t="s">
+      <c r="C14" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="102" t="s">
+      <c r="D14" s="101" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3943,20 +3975,20 @@
     <row r="17" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C17" s="32">
         <f>+(VLOOKUP(C6,$K$4:$P$8,6,0)/$C$11)*VLOOKUP(C14,$L$4:$P$8,4,0)*IF(C11&gt;1,2,1)</f>
-        <v>1.1826000000000001</v>
+        <v>0.7209000000000001</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="20"/>
       <c r="H17" s="32">
         <f>+C17</f>
-        <v>1.1826000000000001</v>
+        <v>0.7209000000000001</v>
       </c>
       <c r="I17" s="33"/>
       <c r="J17" s="20"/>
-      <c r="L17" s="95">
+      <c r="L17" s="94">
         <v>600</v>
       </c>
-      <c r="M17" s="95"/>
+      <c r="M17" s="94"/>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C18" s="24"/>
@@ -3982,24 +4014,29 @@
       <c r="H20" s="24"/>
       <c r="I20" s="25"/>
     </row>
-    <row r="21" spans="3:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C21" s="34">
         <f>SUM(C17:D19)</f>
-        <v>1.3826000000000001</v>
+        <v>0.92090000000000005</v>
       </c>
       <c r="D21" s="35"/>
       <c r="H21" s="34">
         <f>SUM(H17:I19)</f>
-        <v>1.3826000000000001</v>
+        <v>0.92090000000000005</v>
       </c>
       <c r="I21" s="35"/>
       <c r="L21" s="107">
         <f>+H21</f>
-        <v>1.3826000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
+        <v>0.92090000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="L22" s="108"/>
+    </row>
+    <row r="23" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L23" s="108"/>
+    </row>
+    <row r="24" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C24" s="84" t="str">
         <f>CONCATENATE("Custos de impressão + Corte para ",$C$28," 
 capac_nominal: ",VLOOKUP($C$28,$L$4:$N$9,3,0)," chapa/hora
@@ -4022,11 +4059,12 @@
       <c r="I24" s="82"/>
       <c r="J24" s="82"/>
       <c r="K24" s="85"/>
+      <c r="L24" s="108"/>
       <c r="M24" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="3:13" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:13" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C25" s="86"/>
       <c r="D25" s="83"/>
       <c r="E25" s="83"/>
@@ -4035,6 +4073,7 @@
       <c r="I25" s="83"/>
       <c r="J25" s="83"/>
       <c r="K25" s="87"/>
+      <c r="L25" s="108"/>
     </row>
     <row r="26" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C26" s="36" t="s">
@@ -4049,23 +4088,25 @@
       <c r="I26" s="37"/>
       <c r="J26" s="37"/>
       <c r="K26" s="38"/>
+      <c r="L26" s="108"/>
       <c r="M26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C27" s="39"/>
       <c r="E27" s="40"/>
       <c r="F27" s="41"/>
       <c r="H27" s="39"/>
       <c r="J27" s="40"/>
       <c r="K27" s="41"/>
-      <c r="M27" s="89">
+      <c r="L27" s="108"/>
+      <c r="M27" s="105">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C28" s="104" t="str">
+    <row r="28" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C28" s="103" t="str">
         <f>+C14</f>
         <v>Wonder 2</v>
       </c>
@@ -4097,15 +4138,15 @@
         <f>+$J$28/H12</f>
         <v>1.034</v>
       </c>
-      <c r="L28" s="108">
+      <c r="L28" s="109">
         <f>+K28*M27/M28</f>
-        <v>0.62039999999999995</v>
+        <v>1.034</v>
       </c>
       <c r="M28" s="18">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C29" s="66"/>
       <c r="D29" s="40"/>
       <c r="E29" s="40"/>
@@ -4114,12 +4155,13 @@
       <c r="I29" s="40"/>
       <c r="J29" s="40"/>
       <c r="K29" s="41"/>
-      <c r="M29" s="89">
+      <c r="L29" s="108"/>
+      <c r="M29" s="105">
         <v>2500</v>
       </c>
     </row>
-    <row r="30" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="103" t="str">
+    <row r="30" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C30" s="102" t="str">
         <f>IF(D14&lt;&gt;"",D14,"")</f>
         <v>Century</v>
       </c>
@@ -4151,15 +4193,16 @@
         <f>+J30/$H$12*IF($H$12&gt;1,2,1)</f>
         <v>7.0800000000000002E-2</v>
       </c>
-      <c r="L30" s="108">
+      <c r="L30" s="109">
         <f>+(K30*M29/M30)</f>
-        <v>0.17699999999999999</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="M30" s="18">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="31" spans="3:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <f>+M28</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="49">
         <f>SUM(F28:F30)</f>
         <v>1.1048</v>
@@ -4174,10 +4217,11 @@
       <c r="I31" s="50"/>
       <c r="J31" s="47"/>
       <c r="K31" s="48"/>
-      <c r="L31" s="109"/>
-    </row>
-    <row r="32" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M32" s="92"/>
+      <c r="L31" s="110"/>
+    </row>
+    <row r="32" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L32" s="108"/>
+      <c r="M32" s="91"/>
     </row>
     <row r="33" spans="3:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C33" s="36" t="s">
@@ -4192,8 +4236,9 @@
       <c r="I33" s="37"/>
       <c r="J33" s="37"/>
       <c r="K33" s="38"/>
-    </row>
-    <row r="34" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="L33" s="108"/>
+    </row>
+    <row r="34" spans="3:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="39"/>
       <c r="D34" s="40"/>
       <c r="E34" s="40"/>
@@ -4202,11 +4247,12 @@
       <c r="I34" s="40"/>
       <c r="J34" s="40"/>
       <c r="K34" s="41"/>
-      <c r="M34" s="89">
+      <c r="L34" s="108"/>
+      <c r="M34" s="105">
         <v>5000</v>
       </c>
     </row>
-    <row r="35" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C35" s="67" t="str">
         <f>+L8</f>
         <v>Seladora</v>
@@ -4239,22 +4285,23 @@
         <f>+J35*VLOOKUP(H35,$L$4:$M$9,2,0)</f>
         <v>7.0799999999999995E-3</v>
       </c>
-      <c r="L35" s="108">
+      <c r="L35" s="109">
         <f>+(K35*M34/M35)</f>
-        <v>3.5400000000000001E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="M35" s="18">
-        <v>1000</v>
+        <f>+M30</f>
+        <v>600</v>
       </c>
     </row>
     <row r="36" spans="3:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="98">
+      <c r="C36" s="97">
         <f>SUM(F35)</f>
         <v>7.0799999999999995E-3</v>
       </c>
-      <c r="D36" s="99"/>
-      <c r="E36" s="99"/>
-      <c r="F36" s="100"/>
+      <c r="D36" s="98"/>
+      <c r="E36" s="98"/>
+      <c r="F36" s="99"/>
       <c r="H36" s="68">
         <f>SUM(K35)</f>
         <v>7.0799999999999995E-3</v>
@@ -4262,27 +4309,27 @@
       <c r="I36" s="69"/>
       <c r="J36" s="69"/>
       <c r="K36" s="70"/>
-      <c r="M36" s="93"/>
+      <c r="M36" s="92"/>
     </row>
     <row r="37" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C37" s="101">
+      <c r="C37" s="100">
         <f>+C36+C31</f>
         <v>1.11188</v>
       </c>
-      <c r="D37" s="101"/>
-      <c r="E37" s="101"/>
-      <c r="F37" s="101"/>
-      <c r="H37" s="101">
+      <c r="D37" s="100"/>
+      <c r="E37" s="100"/>
+      <c r="F37" s="100"/>
+      <c r="H37" s="100">
         <f>+H36+H31</f>
         <v>1.11188</v>
       </c>
-      <c r="I37" s="101"/>
-      <c r="J37" s="101"/>
-      <c r="K37" s="101"/>
-      <c r="L37" s="105"/>
-      <c r="M37" s="105"/>
-      <c r="N37" s="105"/>
-      <c r="O37" s="105"/>
+      <c r="I37" s="100"/>
+      <c r="J37" s="100"/>
+      <c r="K37" s="100"/>
+      <c r="L37" s="104"/>
+      <c r="M37" s="104"/>
+      <c r="N37" s="104"/>
+      <c r="O37" s="104"/>
     </row>
     <row r="38" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="3:16" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4308,28 +4355,28 @@
       </c>
     </row>
     <row r="40" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C41" s="55">
         <f>+C21+C31+C36+C39</f>
-        <v>2.7944800000000001</v>
+        <v>2.3327800000000001</v>
       </c>
       <c r="D41" s="56"/>
       <c r="E41" s="56"/>
       <c r="F41" s="57"/>
       <c r="H41" s="55">
         <f>+H21+H31+H36+H39</f>
-        <v>2.7944800000000001</v>
+        <v>2.3327800000000001</v>
       </c>
       <c r="I41" s="56"/>
       <c r="J41" s="56"/>
       <c r="K41" s="57"/>
-      <c r="L41" s="110">
+      <c r="L41" s="111">
         <f>SUM(L28:L30,L35,L39+L21)</f>
-        <v>2.5154000000000001</v>
+        <v>2.6089000000000002</v>
       </c>
       <c r="M41" s="55">
         <f>+H21+M30+M36+M39</f>
-        <v>1001.6826</v>
+        <v>601.22089999999992</v>
       </c>
       <c r="N41" s="56"/>
       <c r="O41" s="56"/>
@@ -4349,7 +4396,7 @@
       <c r="I43" s="59"/>
       <c r="J43" s="59"/>
       <c r="K43" s="60"/>
-      <c r="M43" s="90">
+      <c r="M43" s="89">
         <f>+H43</f>
         <v>0.1</v>
       </c>
@@ -4406,32 +4453,32 @@
     <row r="48" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C48" s="61">
         <f>+C41/(1-C43)</f>
-        <v>3.1049777777777776</v>
+        <v>2.5919777777777777</v>
       </c>
       <c r="D48" s="62"/>
       <c r="E48" s="62"/>
       <c r="F48" s="63"/>
       <c r="H48" s="61">
         <f>+H41/(1-H43)</f>
-        <v>3.1049777777777776</v>
+        <v>2.5919777777777777</v>
       </c>
       <c r="I48" s="62"/>
       <c r="J48" s="62"/>
       <c r="K48" s="63"/>
       <c r="L48" s="106">
         <f>+L41*(1+H43)</f>
-        <v>2.7669400000000004</v>
+        <v>2.8697900000000005</v>
       </c>
       <c r="M48" s="61">
         <f>+M41/(1-M43)</f>
-        <v>1112.9806666666666</v>
+        <v>668.0232222222221</v>
       </c>
       <c r="N48" s="62"/>
       <c r="O48" s="62"/>
       <c r="P48" s="63"/>
     </row>
     <row r="49" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L49" s="91"/>
+      <c r="L49" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="37">

--- a/appOrcam/static/arquivos/Preco_m2 esfiha e kibe Onda E (version 1).xlsx
+++ b/appOrcam/static/arquivos/Preco_m2 esfiha e kibe Onda E (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\Documents\GitHub\Dj_srcx_Orcamento\appOrcam\static\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{84A79ADB-0EF6-401E-8379-A426B6C19800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE837BF-F091-486C-8483-A6E7917BF448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{67754E85-EF51-4CB9-B61E-3CED47B47D87}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Calculos Referencias" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -57,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="58">
   <si>
     <t>id</t>
   </si>
@@ -222,13 +221,22 @@
   </si>
   <si>
     <t xml:space="preserve">área aparas </t>
+  </si>
+  <si>
+    <t>Caixa 65 - Chapa 65x85</t>
+  </si>
+  <si>
+    <t>xxx</t>
+  </si>
+  <si>
+    <t>categoria</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="24">
+  <numFmts count="25">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0\ &quot;     unid/chapa&quot;\ "/>
@@ -249,12 +257,13 @@
     <numFmt numFmtId="180" formatCode="&quot;Markup sobre custos: &quot;0%"/>
     <numFmt numFmtId="181" formatCode="&quot;R$&quot;\ #,##0.00\ &quot;preço final com margem por unidade&quot;"/>
     <numFmt numFmtId="182" formatCode="&quot;R$&quot;\ #,##0.000\ &quot;por chapa&quot;"/>
-    <numFmt numFmtId="184" formatCode="&quot;R$&quot;\ #,##0.000\ &quot;seladora&quot;"/>
-    <numFmt numFmtId="185" formatCode="&quot;R$&quot;\ #,##0.000"/>
-    <numFmt numFmtId="187" formatCode="&quot;Csuto de fabricação: &quot;\ &quot;R$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="188" formatCode="&quot;Capac_nominal: &quot;#,##0\ &quot;unidades&quot;"/>
+    <numFmt numFmtId="183" formatCode="&quot;R$&quot;\ #,##0.000\ &quot;seladora&quot;"/>
+    <numFmt numFmtId="184" formatCode="&quot;R$&quot;\ #,##0.000"/>
+    <numFmt numFmtId="185" formatCode="&quot;Csuto de fabricação: &quot;\ &quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="186" formatCode="&quot;Capac_nominal: &quot;#,##0\ &quot;unidades&quot;"/>
+    <numFmt numFmtId="188" formatCode="&quot;Perda &quot;\ &quot;R$&quot;\ #,##0.00\ &quot;por unidade&quot;"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -436,6 +445,14 @@
     <font>
       <sz val="14"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -670,7 +687,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -1080,6 +1097,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1127,7 +1155,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1195,42 +1223,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="171" fontId="19" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="171" fontId="19" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
@@ -1251,113 +1243,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="19" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="19" fillId="33" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="16" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="33" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="179" fontId="16" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="179" fontId="16" fillId="33" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="179" fontId="16" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="180" fontId="19" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="19" fillId="33" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="19" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="20" fillId="34" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="20" fillId="34" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="20" fillId="34" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="19" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="184" fontId="19" fillId="33" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="184" fontId="19" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="172" fontId="16" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="21" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1366,42 +1262,178 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="21" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="20" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="184" fontId="19" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="184" fontId="19" fillId="33" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="184" fontId="19" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="187" fontId="16" fillId="38" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="38" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="187" fontId="16" fillId="38" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="185" fontId="16" fillId="38" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="24" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="171" fontId="20" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="185" fontId="20" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="185" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="184" fontId="20" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="20" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="179" fontId="16" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="179" fontId="16" fillId="33" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="179" fontId="16" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="181" fontId="20" fillId="34" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="20" fillId="34" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="20" fillId="34" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="16" fillId="38" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="19" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="19" fillId="33" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="19" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="19" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="19" fillId="33" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="19" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="183" fontId="19" fillId="33" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="183" fontId="19" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="33" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="19" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="183" fontId="19" fillId="33" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="183" fontId="19" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="188" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="186" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="21" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1466,75 +1498,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="Retângulo 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFD3FD65-4AEC-143E-759D-94C734B1F6A6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3228976" y="2609850"/>
-          <a:ext cx="1409700" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>24654</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>139513</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>663388</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>139514</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1437155</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>25213</xdr:rowOff>
+      <xdr:colOff>1358713</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>25214</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1549,7 +1522,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1346948" y="2627219"/>
+          <a:off x="1268506" y="2817720"/>
           <a:ext cx="1412501" cy="345141"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1589,15 +1562,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>713254</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>195543</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>56030</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>33617</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1612,8 +1585,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1266825" y="5953125"/>
-          <a:ext cx="1990725" cy="257175"/>
+          <a:off x="1318372" y="6437219"/>
+          <a:ext cx="1964952" cy="308722"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1648,15 +1621,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>657226</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>121583</xdr:rowOff>
+      <xdr:colOff>663388</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>121584</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>24655</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>713254</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>114579</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1673,13 +1646,13 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm rot="10800000" flipV="1">
-          <a:off x="1262344" y="2799789"/>
-          <a:ext cx="84605" cy="3373811"/>
+        <a:xfrm rot="10800000" flipH="1" flipV="1">
+          <a:off x="1268506" y="2990290"/>
+          <a:ext cx="49866" cy="3601289"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 370197"/>
+            <a:gd name="adj1" fmla="val -458429"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -1707,13 +1680,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>110941</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>704851</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>87129</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1729,8 +1702,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipH="1" flipV="1">
-          <a:off x="620947" y="3230518"/>
-          <a:ext cx="3943070" cy="2679327"/>
+          <a:off x="492079" y="3549886"/>
+          <a:ext cx="4200806" cy="2679327"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector4">
           <a:avLst>
@@ -1768,15 +1741,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>647699</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>78440</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>44823</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1791,8 +1764,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1257300" y="6343650"/>
-          <a:ext cx="1990725" cy="257175"/>
+          <a:off x="1252817" y="6846794"/>
+          <a:ext cx="2052917" cy="347382"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3004,7 +2977,7 @@
     </row>
     <row r="24" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L25" s="27" t="s">
+      <c r="L25" s="61" t="s">
         <v>25</v>
       </c>
       <c r="M25" t="s">
@@ -3032,7 +3005,7 @@
       </c>
     </row>
     <row r="26" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L26" s="27"/>
+      <c r="L26" s="61"/>
       <c r="M26" t="s">
         <v>14</v>
       </c>
@@ -3058,7 +3031,7 @@
       </c>
     </row>
     <row r="27" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L27" s="27"/>
+      <c r="L27" s="61"/>
       <c r="M27" t="s">
         <v>15</v>
       </c>
@@ -3084,7 +3057,7 @@
       </c>
     </row>
     <row r="28" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L28" s="27"/>
+      <c r="L28" s="61"/>
       <c r="M28" t="s">
         <v>16</v>
       </c>
@@ -3110,7 +3083,7 @@
       </c>
     </row>
     <row r="29" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L29" s="27"/>
+      <c r="L29" s="61"/>
       <c r="M29" t="s">
         <v>17</v>
       </c>
@@ -3136,7 +3109,7 @@
       </c>
     </row>
     <row r="30" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L30" s="27"/>
+      <c r="L30" s="61"/>
       <c r="M30" t="s">
         <v>18</v>
       </c>
@@ -3162,7 +3135,7 @@
       </c>
     </row>
     <row r="34" spans="11:18" x14ac:dyDescent="0.25">
-      <c r="K34" s="27" t="s">
+      <c r="K34" s="61" t="s">
         <v>31</v>
       </c>
       <c r="L34" t="s">
@@ -3176,7 +3149,7 @@
       </c>
     </row>
     <row r="35" spans="11:18" x14ac:dyDescent="0.25">
-      <c r="K35" s="27"/>
+      <c r="K35" s="61"/>
       <c r="L35">
         <v>1</v>
       </c>
@@ -3191,7 +3164,7 @@
       </c>
     </row>
     <row r="36" spans="11:18" x14ac:dyDescent="0.25">
-      <c r="K36" s="27"/>
+      <c r="K36" s="61"/>
       <c r="L36">
         <v>2</v>
       </c>
@@ -3206,7 +3179,7 @@
       </c>
     </row>
     <row r="37" spans="11:18" x14ac:dyDescent="0.25">
-      <c r="K37" s="27"/>
+      <c r="K37" s="61"/>
       <c r="L37">
         <v>3</v>
       </c>
@@ -3215,7 +3188,7 @@
       </c>
     </row>
     <row r="38" spans="11:18" x14ac:dyDescent="0.25">
-      <c r="K38" s="27"/>
+      <c r="K38" s="61"/>
       <c r="L38">
         <v>4</v>
       </c>
@@ -3224,7 +3197,7 @@
       </c>
     </row>
     <row r="39" spans="11:18" x14ac:dyDescent="0.25">
-      <c r="K39" s="27"/>
+      <c r="K39" s="61"/>
       <c r="L39">
         <v>5</v>
       </c>
@@ -3633,7 +3606,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C914D7-4908-4B69-8B97-2FE5B87DEA2C}">
-  <dimension ref="B2:P49"/>
+  <dimension ref="B2:P62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
@@ -3655,12 +3628,12 @@
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="M2" s="95"/>
-      <c r="N2" s="96" t="s">
+      <c r="M2" s="50"/>
+      <c r="N2" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -3687,16 +3660,16 @@
       <c r="J3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="M3" s="96" t="s">
+      <c r="M3" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="N3" s="96" t="s">
+      <c r="N3" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="96" t="s">
+      <c r="O3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="96" t="s">
+      <c r="P3" s="51" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3723,7 +3696,7 @@
         <f>((D4-2*$G$2)*(E4-2*$G$2))/10000</f>
         <v>0.22439999999999999</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="K4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="L4" t="s">
@@ -3736,7 +3709,7 @@
         <v>1000</v>
       </c>
       <c r="O4" s="1">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="P4" s="3">
         <f>+D4/100*E4/100</f>
@@ -3763,10 +3736,10 @@
         <v>1</v>
       </c>
       <c r="J5" s="3">
-        <f t="shared" ref="J5:J8" si="0">((D5-2*$G$2)*(E5-2*$G$2))/10000</f>
+        <f t="shared" ref="J5:J10" si="0">((D5-2*$G$2)*(E5-2*$G$2))/10000</f>
         <v>0.2964</v>
       </c>
-      <c r="K5" s="95" t="s">
+      <c r="K5" s="50" t="s">
         <v>8</v>
       </c>
       <c r="L5" t="s">
@@ -3779,7 +3752,7 @@
         <v>600</v>
       </c>
       <c r="O5" s="1">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="P5" s="3">
         <f>+D5/100*E5/100</f>
@@ -3809,7 +3782,7 @@
         <f t="shared" si="0"/>
         <v>0.37840000000000001</v>
       </c>
-      <c r="K6" s="95" t="s">
+      <c r="K6" s="50" t="s">
         <v>9</v>
       </c>
       <c r="L6" t="s">
@@ -3822,7 +3795,7 @@
         <v>600</v>
       </c>
       <c r="O6" s="1">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="P6" s="3">
         <f>+D6/100*E6/100</f>
@@ -3852,7 +3825,7 @@
         <f t="shared" si="0"/>
         <v>0.47039999999999998</v>
       </c>
-      <c r="K7" s="95" t="s">
+      <c r="K7" s="50" t="s">
         <v>10</v>
       </c>
       <c r="L7" t="s">
@@ -3865,7 +3838,7 @@
         <v>2500</v>
       </c>
       <c r="O7" s="1">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="P7" s="3">
         <f>+D7/100*E7/100</f>
@@ -3895,7 +3868,7 @@
         <f t="shared" si="0"/>
         <v>0.57240000000000002</v>
       </c>
-      <c r="K8" s="95" t="s">
+      <c r="K8" s="50" t="s">
         <v>11</v>
       </c>
       <c r="L8" t="s">
@@ -3908,14 +3881,39 @@
         <v>5000</v>
       </c>
       <c r="O8" s="1">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="P8" s="3">
         <f>+D8/100*E8/100</f>
         <v>0.60500000000000009</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="1">
+        <v>65</v>
+      </c>
+      <c r="E9" s="1">
+        <v>85</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3">
+        <f>((D9-2*$G$2)*(E9-2*$G$2))/10000</f>
+        <v>0.52290000000000003</v>
+      </c>
+      <c r="K9" s="112" t="s">
+        <v>56</v>
+      </c>
       <c r="L9" t="s">
         <v>45</v>
       </c>
@@ -3925,600 +3923,645 @@
       <c r="N9" s="26">
         <v>300</v>
       </c>
+      <c r="P9" s="3">
+        <f>+D9/100*E9/100</f>
+        <v>0.55249999999999999</v>
+      </c>
     </row>
     <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D10" t="s">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="J10" s="3"/>
+      <c r="K10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="P10" s="3">
+        <f>+D9/100*E9/100</f>
+        <v>0.55249999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="80">
+      <c r="F11" s="42">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="88">
-        <v>1</v>
-      </c>
-    </row>
     <row r="12" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D12" s="23"/>
-      <c r="H12" s="88">
-        <f>+C11</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C13" s="22"/>
+      <c r="C12" s="44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D13" s="23"/>
-    </row>
-    <row r="14" spans="2:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="C14" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="101" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-    </row>
-    <row r="16" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="28" t="s">
+      <c r="H13" s="44">
+        <f>+C12</f>
+        <v>4</v>
+      </c>
+      <c r="K13">
+        <f>+(VLOOKUP(C9,$K$4:$P$10,6,0)/$C$12)</f>
+        <v>0.138125</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C14" s="22"/>
+      <c r="D14" s="23"/>
+      <c r="K14">
+        <f>+VLOOKUP(C15,$L$4:$P$10,4,0)</f>
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="21" x14ac:dyDescent="0.35">
+      <c r="C15" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="52"/>
+    </row>
+    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="J16">
+        <f>+P9/9</f>
+        <v>6.1388888888888889E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="29"/>
-      <c r="H16" s="28" t="s">
+      <c r="D17" s="94"/>
+      <c r="H17" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="29"/>
-    </row>
-    <row r="17" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C17" s="32">
-        <f>+(VLOOKUP(C6,$K$4:$P$8,6,0)/$C$11)*VLOOKUP(C14,$L$4:$P$8,4,0)*IF(C11&gt;1,2,1)</f>
-        <v>0.7209000000000001</v>
-      </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="20"/>
-      <c r="H17" s="32">
-        <f>+C17</f>
-        <v>0.7209000000000001</v>
-      </c>
-      <c r="I17" s="33"/>
-      <c r="J17" s="20"/>
-      <c r="L17" s="94">
-        <v>600</v>
-      </c>
-      <c r="M17" s="94"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C18" s="24"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="21"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="21"/>
+      <c r="I17" s="94"/>
+    </row>
+    <row r="18" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C18" s="95">
+        <f>+(VLOOKUP(C6,$K$4:$P$10,6,0)/$C$12)*VLOOKUP(C15,$L$4:$P$10,4,0)*IF(C12&gt;1,1,1)</f>
+        <v>0.29565000000000002</v>
+      </c>
+      <c r="D18" s="96"/>
+      <c r="H18" s="95">
+        <f>+C18</f>
+        <v>0.29565000000000002</v>
+      </c>
+      <c r="I18" s="96"/>
+      <c r="J18" s="20"/>
+      <c r="L18" s="68">
+        <v>1000</v>
+      </c>
+      <c r="M18" s="68"/>
     </row>
     <row r="19" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C19" s="30">
+      <c r="C19" s="24"/>
+      <c r="D19" s="25"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="21"/>
+    </row>
+    <row r="20" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C20" s="97">
         <v>0.2</v>
       </c>
-      <c r="D19" s="31"/>
-      <c r="H19" s="30">
+      <c r="D20" s="98"/>
+      <c r="H20" s="97">
         <v>0.2</v>
       </c>
-      <c r="I19" s="31"/>
-    </row>
-    <row r="20" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="24"/>
-      <c r="D20" s="25"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="25"/>
-    </row>
-    <row r="21" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="34">
-        <f>SUM(C17:D19)</f>
-        <v>0.92090000000000005</v>
-      </c>
-      <c r="D21" s="35"/>
-      <c r="H21" s="34">
-        <f>SUM(H17:I19)</f>
-        <v>0.92090000000000005</v>
-      </c>
-      <c r="I21" s="35"/>
-      <c r="L21" s="107">
-        <f>+H21</f>
-        <v>0.92090000000000005</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="L22" s="108"/>
-    </row>
-    <row r="23" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L23" s="108"/>
-    </row>
-    <row r="24" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C24" s="84" t="str">
-        <f>CONCATENATE("Custos de impressão + Corte para ",$C$28," 
-capac_nominal: ",VLOOKUP($C$28,$L$4:$N$9,3,0)," chapa/hora
-pedido de ",VLOOKUP($C$28,$L$4:$N$9,3,0)," caixas")</f>
-        <v>Custos de impressão + Corte para Wonder 2 
-capac_nominal: 600 chapa/hora
-pedido de 600 caixas</v>
-      </c>
-      <c r="D24" s="82"/>
-      <c r="E24" s="82"/>
-      <c r="F24" s="85"/>
-      <c r="H24" s="84" t="str">
-        <f>CONCATENATE("Custos de impressão + Corte para ",$C$28," 
-capac_nominal: ",VLOOKUP($C$28,$L$4:$N$9,3,0)," chapa/hora
-pedido de ",L17," caixas")</f>
-        <v>Custos de impressão + Corte para Wonder 2 
-capac_nominal: 600 chapa/hora
-pedido de 600 caixas</v>
-      </c>
-      <c r="I24" s="82"/>
-      <c r="J24" s="82"/>
-      <c r="K24" s="85"/>
-      <c r="L24" s="108"/>
-      <c r="M24" t="s">
+      <c r="I20" s="98"/>
+      <c r="L20" s="110">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="24"/>
+      <c r="D21" s="25"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="25"/>
+    </row>
+    <row r="22" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C22" s="99">
+        <f>SUM(C18:D20)</f>
+        <v>0.49565000000000003</v>
+      </c>
+      <c r="D22" s="100"/>
+      <c r="H22" s="99">
+        <f>SUM(H18:I20)</f>
+        <v>0.49565000000000003</v>
+      </c>
+      <c r="I22" s="100"/>
+      <c r="L22" s="56">
+        <f>+H22</f>
+        <v>0.49565000000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="L23" s="57"/>
+    </row>
+    <row r="24" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L24" s="57"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C25" s="101" t="str">
+        <f>CONCATENATE("Custos de impressão + Corte para ",$C$29," 
+capac_nominal: ",VLOOKUP($C$29,$L$4:$N$9,3,0)," chapa/hora
+pedido de ",VLOOKUP($C$29,$L$4:$N$9,3,0)," caixas")</f>
+        <v>Custos de impressão + Corte para Flexo 
+capac_nominal: 1000 chapa/hora
+pedido de 1000 caixas</v>
+      </c>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="103"/>
+      <c r="H25" s="101" t="str">
+        <f>CONCATENATE("Custos de impressão + Corte para ",$C$29," 
+capac_nominal: ",VLOOKUP($C$29,$L$4:$N$9,3,0)," chapa/hora
+pedido de ",L18," caixas")</f>
+        <v>Custos de impressão + Corte para Flexo 
+capac_nominal: 1000 chapa/hora
+pedido de 1000 caixas</v>
+      </c>
+      <c r="I25" s="102"/>
+      <c r="J25" s="102"/>
+      <c r="K25" s="103"/>
+      <c r="M25" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="3:13" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="86"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="87"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="87"/>
-      <c r="L25" s="108"/>
-    </row>
-    <row r="26" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C26" s="36" t="s">
+    <row r="26" spans="3:13" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="104"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="106"/>
+      <c r="H26" s="104"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="105"/>
+      <c r="K26" s="106"/>
+    </row>
+    <row r="27" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C27" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="38"/>
-      <c r="H26" s="36" t="s">
+      <c r="D27" s="85"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="86"/>
+      <c r="H27" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="108"/>
-      <c r="M26" t="s">
+      <c r="I27" s="85"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="86"/>
+      <c r="L27" s="57"/>
+      <c r="M27" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C27" s="39"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="41"/>
-      <c r="H27" s="39"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="108"/>
-      <c r="M27" s="105">
-        <v>600</v>
-      </c>
-    </row>
     <row r="28" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C28" s="103" t="str">
-        <f>+C14</f>
-        <v>Wonder 2</v>
-      </c>
-      <c r="D28" s="42">
-        <f>+$F$10/VLOOKUP(C28,$L$4:$N$9,3,0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="E28" s="43">
-        <f>+D28*VLOOKUP(C28,$L$4:$M$9,2,0)</f>
-        <v>1.034</v>
-      </c>
-      <c r="F28" s="44">
-        <f>+$E$28/C11</f>
-        <v>1.034</v>
-      </c>
-      <c r="H28" s="81" t="str">
-        <f>+C14</f>
-        <v>Wonder 2</v>
-      </c>
-      <c r="I28" s="42">
-        <f>+$F$10/VLOOKUP(H28,$L$4:$N$9,3,0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="J28" s="43">
-        <f>+I28*VLOOKUP(H28,$L$4:$M$9,2,0)</f>
-        <v>1.034</v>
-      </c>
-      <c r="K28" s="44">
-        <f>+$J$28/H12</f>
-        <v>1.034</v>
-      </c>
-      <c r="L28" s="109">
-        <f>+K28*M27/M28</f>
-        <v>1.034</v>
-      </c>
-      <c r="M28" s="18">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="29" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C29" s="66"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="41"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="105">
+      <c r="C28" s="27"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="29"/>
+      <c r="H28" s="27"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="113">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" ht="21" x14ac:dyDescent="0.35">
+      <c r="C29" s="114" t="str">
+        <f>+C15</f>
+        <v>Flexo</v>
+      </c>
+      <c r="D29" s="30">
+        <f>+$F$11/VLOOKUP(C29,$L$4:$N$9,3,0)</f>
+        <v>0.06</v>
+      </c>
+      <c r="E29" s="31">
+        <f>+D29*VLOOKUP(C29,$L$4:$M$9,2,0)</f>
+        <v>0.44279999999999997</v>
+      </c>
+      <c r="F29" s="32">
+        <f>+$E$29/C12</f>
+        <v>0.11069999999999999</v>
+      </c>
+      <c r="H29" s="43" t="str">
+        <f>+C15</f>
+        <v>Flexo</v>
+      </c>
+      <c r="I29" s="30">
+        <f>+$F$11/VLOOKUP(H29,$L$4:$N$9,3,0)</f>
+        <v>0.06</v>
+      </c>
+      <c r="J29" s="31">
+        <f>+I29*VLOOKUP(H29,$L$4:$M$9,2,0)</f>
+        <v>0.44279999999999997</v>
+      </c>
+      <c r="K29" s="32">
+        <f>+$J$29/H13</f>
+        <v>0.11069999999999999</v>
+      </c>
+      <c r="L29" s="58">
+        <f>+K29*M28/M29</f>
+        <v>0.11069999999999999</v>
+      </c>
+      <c r="M29" s="18">
+        <f>+L18</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C30" s="40"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="29"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="29"/>
+      <c r="M30" s="54">
         <v>2500</v>
       </c>
     </row>
-    <row r="30" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C30" s="102" t="str">
-        <f>IF(D14&lt;&gt;"",D14,"")</f>
-        <v>Century</v>
-      </c>
-      <c r="D30" s="42">
-        <f>IF(C30&lt;&gt;"",($F$10/VLOOKUP(C30,$L$4:$N$9,3,0)),0)</f>
-        <v>2.4E-2</v>
-      </c>
-      <c r="E30" s="43">
-        <f>IF(D30&gt;0,(D30*VLOOKUP(C30,$L$4:$M$9,2,0)),0)</f>
-        <v>7.0800000000000002E-2</v>
-      </c>
-      <c r="F30" s="46">
-        <f>+E30/$C$11*IF($C$11&gt;1,2,1)</f>
-        <v>7.0800000000000002E-2</v>
-      </c>
-      <c r="H30" s="67" t="str">
-        <f>IF(D14&lt;&gt;"",D14,"")</f>
-        <v>Century</v>
-      </c>
-      <c r="I30" s="42">
-        <f>IF(H30&lt;&gt;"",($F$10/VLOOKUP(H30,$L$4:$N$9,3,0)),0)</f>
-        <v>2.4E-2</v>
-      </c>
-      <c r="J30" s="43">
-        <f>IF(I30&gt;0,(I30*VLOOKUP(H30,$L$4:$M$9,2,0)),0)</f>
-        <v>7.0800000000000002E-2</v>
-      </c>
-      <c r="K30" s="46">
-        <f>+J30/$H$12*IF($H$12&gt;1,2,1)</f>
-        <v>7.0800000000000002E-2</v>
-      </c>
-      <c r="L30" s="109">
-        <f>+(K30*M29/M30)</f>
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="M30" s="18">
-        <f>+M28</f>
-        <v>600</v>
-      </c>
-    </row>
     <row r="31" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C31" s="49">
-        <f>SUM(F28:F30)</f>
-        <v>1.1048</v>
-      </c>
-      <c r="D31" s="50"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="48"/>
-      <c r="H31" s="49">
-        <f>SUM(K28:K30)</f>
-        <v>1.1048</v>
-      </c>
-      <c r="I31" s="50"/>
-      <c r="J31" s="47"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="110"/>
+      <c r="C31" s="115" t="str">
+        <f>IF(D15&lt;&gt;"",D15,"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="30">
+        <f>IF(C31&lt;&gt;"",($F$11/VLOOKUP(C31,$L$4:$N$9,3,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="31">
+        <f>IF(D31&gt;0,(D31*VLOOKUP(C31,$L$4:$M$9,2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="34">
+        <f>+E31/$C$12*IF($C$12&gt;1,2,1)</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="41" t="str">
+        <f>IF(D15&lt;&gt;"",D15,"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="30">
+        <f>IF(H31&lt;&gt;"",($F$11/VLOOKUP(H31,$L$4:$N$9,3,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="31">
+        <f>IF(I31&gt;0,(I31*VLOOKUP(H31,$L$4:$M$9,2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="34">
+        <f>+J31/$H$13*IF($H$13&gt;1,2,1)</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="58">
+        <f>+(K31*M30/M31)</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="18">
+        <f>+L18</f>
+        <v>1000</v>
+      </c>
     </row>
     <row r="32" spans="3:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L32" s="108"/>
-      <c r="M32" s="91"/>
-    </row>
-    <row r="33" spans="3:16" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C33" s="36" t="s">
+      <c r="C32" s="82">
+        <f>SUM(F29:F31)</f>
+        <v>0.11069999999999999</v>
+      </c>
+      <c r="D32" s="83"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="36"/>
+      <c r="H32" s="82">
+        <f>SUM(K29:K31)</f>
+        <v>0.11069999999999999</v>
+      </c>
+      <c r="I32" s="83"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="59"/>
+    </row>
+    <row r="33" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L33" s="57"/>
+      <c r="M33" s="47"/>
+    </row>
+    <row r="34" spans="3:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C34" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="38"/>
-      <c r="H33" s="36" t="s">
+      <c r="D34" s="85"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="86"/>
+      <c r="H34" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="I33" s="37"/>
-      <c r="J33" s="37"/>
-      <c r="K33" s="38"/>
-      <c r="L33" s="108"/>
-    </row>
-    <row r="34" spans="3:16" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C34" s="39"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="41"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="108"/>
-      <c r="M34" s="105">
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
+      <c r="K34" s="86"/>
+      <c r="L34" s="57"/>
+    </row>
+    <row r="35" spans="3:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C35" s="27"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="29"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="54">
         <v>5000</v>
       </c>
     </row>
-    <row r="35" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C35" s="67" t="str">
+    <row r="36" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C36" s="41" t="str">
         <f>+L8</f>
         <v>Seladora</v>
       </c>
-      <c r="D35" s="64">
-        <f>VLOOKUP(C35,$L$4:$N$9,3,0)</f>
+      <c r="D36" s="38">
+        <f>VLOOKUP(C36,$L$4:$N$9,3,0)</f>
         <v>5000</v>
       </c>
-      <c r="E35" s="45">
-        <f>+$F$10/VLOOKUP(C35,$L$4:$N$9,3,0)</f>
+      <c r="E36" s="33">
+        <f>+$F$11/VLOOKUP(C36,$L$4:$N$9,3,0)</f>
         <v>1.2E-2</v>
       </c>
-      <c r="F35" s="65">
-        <f>+E35*VLOOKUP(C35,$L$4:$M$9,2,0)</f>
+      <c r="F36" s="39">
+        <f>+E36*VLOOKUP(C36,$L$4:$M$9,2,0)</f>
         <v>7.0799999999999995E-3</v>
       </c>
-      <c r="H35" s="67" t="str">
+      <c r="H36" s="41" t="str">
         <f>+L8</f>
         <v>Seladora</v>
       </c>
-      <c r="I35" s="64">
-        <f>VLOOKUP(H35,$L$4:$N$9,3,0)</f>
+      <c r="I36" s="38">
+        <f>VLOOKUP(H36,$L$4:$N$9,3,0)</f>
         <v>5000</v>
       </c>
-      <c r="J35" s="45">
-        <f>+$F$10/VLOOKUP(H35,$L$4:$N$9,3,0)</f>
+      <c r="J36" s="33">
+        <f>+$F$11/VLOOKUP(H36,$L$4:$N$9,3,0)</f>
         <v>1.2E-2</v>
       </c>
-      <c r="K35" s="65">
-        <f>+J35*VLOOKUP(H35,$L$4:$M$9,2,0)</f>
+      <c r="K36" s="39">
+        <f>+J36*VLOOKUP(H36,$L$4:$M$9,2,0)</f>
         <v>7.0799999999999995E-3</v>
       </c>
-      <c r="L35" s="109">
-        <f>+(K35*M34/M35)</f>
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="M35" s="18">
-        <f>+M30</f>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="36" spans="3:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="97">
-        <f>SUM(F35)</f>
+      <c r="L36" s="58">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M36" s="18">
+        <f>+M31</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="37" spans="3:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="107">
+        <f>SUM(F36)</f>
         <v>7.0799999999999995E-3</v>
       </c>
-      <c r="D36" s="98"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="99"/>
-      <c r="H36" s="68">
-        <f>SUM(K35)</f>
+      <c r="D37" s="108"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="109"/>
+      <c r="H37" s="87">
+        <f>SUM(K36)</f>
         <v>7.0799999999999995E-3</v>
       </c>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
-      <c r="K36" s="70"/>
-      <c r="M36" s="92"/>
-    </row>
-    <row r="37" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C37" s="100">
-        <f>+C36+C31</f>
-        <v>1.11188</v>
-      </c>
-      <c r="D37" s="100"/>
-      <c r="E37" s="100"/>
-      <c r="F37" s="100"/>
-      <c r="H37" s="100">
-        <f>+H36+H31</f>
-        <v>1.11188</v>
-      </c>
-      <c r="I37" s="100"/>
-      <c r="J37" s="100"/>
-      <c r="K37" s="100"/>
-      <c r="L37" s="104"/>
-      <c r="M37" s="104"/>
-      <c r="N37" s="104"/>
-      <c r="O37" s="104"/>
-    </row>
-    <row r="38" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="3:16" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="52">
+      <c r="I37" s="88"/>
+      <c r="J37" s="88"/>
+      <c r="K37" s="89"/>
+      <c r="M37" s="48"/>
+    </row>
+    <row r="38" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C38" s="69">
+        <f>+C37+C32</f>
+        <v>0.11778</v>
+      </c>
+      <c r="D38" s="69"/>
+      <c r="E38" s="69"/>
+      <c r="F38" s="69"/>
+      <c r="H38" s="69">
+        <f>+H37+H32</f>
+        <v>0.11778</v>
+      </c>
+      <c r="I38" s="69"/>
+      <c r="J38" s="69"/>
+      <c r="K38" s="69"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="53"/>
+      <c r="N38" s="53"/>
+      <c r="O38" s="53"/>
+    </row>
+    <row r="39" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="3:16" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C40" s="90">
         <v>0.3</v>
       </c>
-      <c r="D39" s="53"/>
-      <c r="E39" s="53"/>
-      <c r="F39" s="54"/>
-      <c r="H39" s="52">
+      <c r="D40" s="91"/>
+      <c r="E40" s="91"/>
+      <c r="F40" s="92"/>
+      <c r="H40" s="90">
         <v>0.3</v>
       </c>
-      <c r="I39" s="53"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="54"/>
-      <c r="L39" s="51">
-        <f>+H39</f>
+      <c r="I40" s="91"/>
+      <c r="J40" s="91"/>
+      <c r="K40" s="92"/>
+      <c r="L40" s="111">
+        <f>+H40</f>
         <v>0.3</v>
       </c>
-      <c r="M39" s="51">
-        <f>+H39</f>
+      <c r="M40" s="37">
+        <f>+H40</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="40" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="55">
-        <f>+C21+C31+C36+C39</f>
-        <v>2.3327800000000001</v>
-      </c>
-      <c r="D41" s="56"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="57"/>
-      <c r="H41" s="55">
-        <f>+H21+H31+H36+H39</f>
-        <v>2.3327800000000001</v>
-      </c>
-      <c r="I41" s="56"/>
-      <c r="J41" s="56"/>
-      <c r="K41" s="57"/>
-      <c r="L41" s="111">
-        <f>SUM(L28:L30,L35,L39+L21)</f>
-        <v>2.6089000000000002</v>
-      </c>
-      <c r="M41" s="55">
-        <f>+H21+M30+M36+M39</f>
-        <v>601.22089999999992</v>
-      </c>
-      <c r="N41" s="56"/>
-      <c r="O41" s="56"/>
-      <c r="P41" s="57"/>
-    </row>
-    <row r="42" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="3:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="58">
+    <row r="41" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C42" s="62">
+        <f>+C22+C32+C37+C40</f>
+        <v>0.91342999999999996</v>
+      </c>
+      <c r="D42" s="63"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="64"/>
+      <c r="H42" s="62">
+        <f>+H22+H32+H37+H40</f>
+        <v>0.91342999999999996</v>
+      </c>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
+      <c r="K42" s="64"/>
+      <c r="L42" s="60">
+        <f>SUM(L20:L41)</f>
+        <v>1.0563500000000001</v>
+      </c>
+      <c r="M42" s="62">
+        <f>+H22+M31+M37+M40</f>
+        <v>1000.7956499999999</v>
+      </c>
+      <c r="N42" s="63"/>
+      <c r="O42" s="63"/>
+      <c r="P42" s="64"/>
+    </row>
+    <row r="43" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="3:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="70">
         <v>0.1</v>
       </c>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="60"/>
-      <c r="H43" s="58">
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="72"/>
+      <c r="H44" s="70">
         <v>0.1</v>
       </c>
-      <c r="I43" s="59"/>
-      <c r="J43" s="59"/>
-      <c r="K43" s="60"/>
-      <c r="M43" s="89">
-        <f>+H43</f>
+      <c r="I44" s="71"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="M44" s="45">
+        <f>+H44</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="44" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C45" s="73" t="str">
-        <f>CONCATENATE("Custos de impressão + Corte para ",$C$28," - capac_nominal: ",VLOOKUP($C$28,$L$4:$N$9,3,0)," chapa/hora")</f>
-        <v>Custos de impressão + Corte para Wonder 2 - capac_nominal: 600 chapa/hora</v>
-      </c>
-      <c r="D45" s="74"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="75"/>
-      <c r="H45" s="73" t="str">
-        <f>CONCATENATE("Custos de impressão + Corte para ",H28," - capac_nominal: ",VLOOKUP(H28,$L$4:$N$9,3,0)," chapa/hora")</f>
-        <v>Custos de impressão + Corte para Wonder 2 - capac_nominal: 600 chapa/hora</v>
-      </c>
-      <c r="I45" s="74"/>
-      <c r="J45" s="74"/>
-      <c r="K45" s="75"/>
-    </row>
+    <row r="45" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C46" s="76" t="str">
-        <f>CONCATENATE("Custos de Corte para ",C30," - capac_nominal: ",VLOOKUP(C30,$L$4:$N$9,3,0)," chapa/hora")</f>
-        <v>Custos de Corte para Century - capac_nominal: 2500 chapa/hora</v>
-      </c>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="77"/>
-      <c r="H46" s="76" t="str">
-        <f>CONCATENATE("Custos de Corte para ",H30," - capac_nominal: ",VLOOKUP(H30,$L$4:$N$9,3,0)," chapa/hora")</f>
-        <v>Custos de Corte para Century - capac_nominal: 2500 chapa/hora</v>
-      </c>
-      <c r="I46" s="71"/>
-      <c r="J46" s="71"/>
-      <c r="K46" s="77"/>
-    </row>
-    <row r="47" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="78" t="str">
-        <f>CONCATENATE("Custos de Embalagem para ",C35," - capac_nominal: ",VLOOKUP(C35,$L$4:$N$9,3,0)," chapa/hora")</f>
+      <c r="C46" s="73" t="str">
+        <f>CONCATENATE("Custos de impressão + Corte para ",$C$29," - capac_nominal: ",VLOOKUP($C$29,$L$4:$N$9,3,0)," chapa/hora")</f>
+        <v>Custos de impressão + Corte para Flexo - capac_nominal: 1000 chapa/hora</v>
+      </c>
+      <c r="D46" s="74"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="75"/>
+      <c r="H46" s="73" t="str">
+        <f>CONCATENATE("Custos de impressão + Corte para ",H29," - capac_nominal: ",VLOOKUP(H29,$L$4:$N$9,3,0)," chapa/hora")</f>
+        <v>Custos de impressão + Corte para Flexo - capac_nominal: 1000 chapa/hora</v>
+      </c>
+      <c r="I46" s="74"/>
+      <c r="J46" s="74"/>
+      <c r="K46" s="75"/>
+    </row>
+    <row r="47" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C47" s="76" t="e">
+        <f>CONCATENATE("Custos de Corte para ",C31," - capac_nominal: ",VLOOKUP(C31,$L$4:$N$9,3,0)," chapa/hora")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
+      <c r="F47" s="78"/>
+      <c r="H47" s="76" t="e">
+        <f>CONCATENATE("Custos de Corte para ",H31," - capac_nominal: ",VLOOKUP(H31,$L$4:$N$9,3,0)," chapa/hora")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I47" s="77"/>
+      <c r="J47" s="77"/>
+      <c r="K47" s="78"/>
+    </row>
+    <row r="48" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="79" t="str">
+        <f>CONCATENATE("Custos de Embalagem para ",C36," - capac_nominal: ",VLOOKUP(C36,$L$4:$N$9,3,0)," chapa/hora")</f>
         <v>Custos de Embalagem para Seladora - capac_nominal: 5000 chapa/hora</v>
       </c>
-      <c r="D47" s="72"/>
-      <c r="E47" s="72"/>
-      <c r="F47" s="79"/>
-      <c r="H47" s="78" t="str">
-        <f>CONCATENATE("Custos de Embalagem para ",H35," - capac_nominal: ",VLOOKUP(H35,$L$4:$N$9,3,0)," chapa/hora")</f>
+      <c r="D48" s="80"/>
+      <c r="E48" s="80"/>
+      <c r="F48" s="81"/>
+      <c r="H48" s="79" t="str">
+        <f>CONCATENATE("Custos de Embalagem para ",H36," - capac_nominal: ",VLOOKUP(H36,$L$4:$N$9,3,0)," chapa/hora")</f>
         <v>Custos de Embalagem para Seladora - capac_nominal: 5000 chapa/hora</v>
       </c>
-      <c r="I47" s="72"/>
-      <c r="J47" s="72"/>
-      <c r="K47" s="79"/>
-    </row>
-    <row r="48" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C48" s="61">
-        <f>+C41/(1-C43)</f>
-        <v>2.5919777777777777</v>
-      </c>
-      <c r="D48" s="62"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="63"/>
-      <c r="H48" s="61">
-        <f>+H41/(1-H43)</f>
-        <v>2.5919777777777777</v>
-      </c>
-      <c r="I48" s="62"/>
-      <c r="J48" s="62"/>
-      <c r="K48" s="63"/>
-      <c r="L48" s="106">
-        <f>+L41*(1+H43)</f>
-        <v>2.8697900000000005</v>
-      </c>
-      <c r="M48" s="61">
-        <f>+M41/(1-M43)</f>
-        <v>668.0232222222221</v>
-      </c>
-      <c r="N48" s="62"/>
-      <c r="O48" s="62"/>
-      <c r="P48" s="63"/>
-    </row>
-    <row r="49" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L49" s="90"/>
+      <c r="I48" s="80"/>
+      <c r="J48" s="80"/>
+      <c r="K48" s="81"/>
+    </row>
+    <row r="49" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C49" s="65">
+        <f>+C42/(1-C44)</f>
+        <v>1.0149222222222221</v>
+      </c>
+      <c r="D49" s="66"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="67"/>
+      <c r="H49" s="65">
+        <f>+H42/(1-H44)</f>
+        <v>1.0149222222222221</v>
+      </c>
+      <c r="I49" s="66"/>
+      <c r="J49" s="66"/>
+      <c r="K49" s="67"/>
+      <c r="L49" s="55">
+        <f>+L42*(1+H44)</f>
+        <v>1.1619850000000003</v>
+      </c>
+      <c r="M49" s="65">
+        <f>+M42/(1-M44)</f>
+        <v>1111.9951666666666</v>
+      </c>
+      <c r="N49" s="66"/>
+      <c r="O49" s="66"/>
+      <c r="P49" s="67"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="L50" s="46"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C60" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C61" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C62" t="s">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="M41:P41"/>
-    <mergeCell ref="M48:P48"/>
-    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C25:F26"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="C34:F34"/>
     <mergeCell ref="C37:F37"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="H25:K26"/>
+    <mergeCell ref="M42:P42"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="H44:K44"/>
     <mergeCell ref="H46:K46"/>
     <mergeCell ref="H47:K47"/>
     <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="H24:K25"/>
-    <mergeCell ref="C43:F43"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C41:F41"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C24:F25"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="C44:F44"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
